--- a/dataProcess/rawData/bilibili_tasks.xlsx
+++ b/dataProcess/rawData/bilibili_tasks.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VS\4C_Frontend\dataProcess\rawData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C893E7D-BF4B-4CDF-A8FB-F54B0F6DB557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23152" windowHeight="11055"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11829" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="257">
   <si>
     <t>bvid</t>
   </si>
@@ -768,19 +774,46 @@
   </si>
   <si>
     <t>BV1PR4y1u71z</t>
+  </si>
+  <si>
+    <t>status</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>processed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>unprocessed</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BV1aW4y197nn</t>
+  </si>
+  <si>
+    <t>BV1Co4y1o7m6</t>
+  </si>
+  <si>
+    <t>unprocessed</t>
+  </si>
+  <si>
+    <t>BV1jx411x7QC</t>
+  </si>
+  <si>
+    <t>BV1awSmYDEkW</t>
+  </si>
+  <si>
+    <t>BV1v7411T798</t>
+  </si>
+  <si>
+    <t>BV16x411n7Zy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -796,352 +829,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1149,251 +859,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1407,65 +875,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1743,22 +1167,23 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C174"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D180"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.149999999999999" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.212389380531" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.4247787610619" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5044247787611" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.14159292035398" style="2"/>
+    <col min="1" max="1" width="22.2109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.2109375" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1768,8 +1193,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1779,8 +1207,11 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1790,8 +1221,11 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1801,8 +1235,11 @@
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1812,8 +1249,11 @@
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1823,8 +1263,11 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1834,8 +1277,11 @@
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -1845,8 +1291,11 @@
       <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -1856,8 +1305,11 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -1867,8 +1319,11 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -1878,8 +1333,11 @@
       <c r="C11" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1889,8 +1347,11 @@
       <c r="C12" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -1900,8 +1361,11 @@
       <c r="C13" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -1911,8 +1375,11 @@
       <c r="C14" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -1922,8 +1389,11 @@
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1933,8 +1403,11 @@
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -1944,8 +1417,11 @@
       <c r="C17" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>25</v>
       </c>
@@ -1955,8 +1431,11 @@
       <c r="C18" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
@@ -1966,8 +1445,11 @@
       <c r="C19" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>29</v>
       </c>
@@ -1977,8 +1459,11 @@
       <c r="C20" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -1988,8 +1473,11 @@
       <c r="C21" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>31</v>
       </c>
@@ -1999,8 +1487,11 @@
       <c r="C22" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -2010,8 +1501,11 @@
       <c r="C23" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>34</v>
       </c>
@@ -2021,8 +1515,11 @@
       <c r="C24" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>35</v>
       </c>
@@ -2032,8 +1529,11 @@
       <c r="C25" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>36</v>
       </c>
@@ -2043,8 +1543,11 @@
       <c r="C26" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
@@ -2054,8 +1557,11 @@
       <c r="C27" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
@@ -2065,8 +1571,11 @@
       <c r="C28" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>41</v>
       </c>
@@ -2076,8 +1585,11 @@
       <c r="C29" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>42</v>
       </c>
@@ -2087,8 +1599,11 @@
       <c r="C30" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>43</v>
       </c>
@@ -2098,8 +1613,11 @@
       <c r="C31" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>45</v>
       </c>
@@ -2109,8 +1627,11 @@
       <c r="C32" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>46</v>
       </c>
@@ -2120,8 +1641,11 @@
       <c r="C33" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>49</v>
       </c>
@@ -2131,8 +1655,11 @@
       <c r="C34" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -2142,8 +1669,11 @@
       <c r="C35" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -2153,8 +1683,11 @@
       <c r="C36" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>52</v>
       </c>
@@ -2164,8 +1697,11 @@
       <c r="C37" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>54</v>
       </c>
@@ -2175,8 +1711,11 @@
       <c r="C38" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="D38" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>55</v>
       </c>
@@ -2186,8 +1725,11 @@
       <c r="C39" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D39" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>58</v>
       </c>
@@ -2197,8 +1739,11 @@
       <c r="C40" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="D40" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>59</v>
       </c>
@@ -2208,8 +1753,11 @@
       <c r="C41" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="D41" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>60</v>
       </c>
@@ -2219,8 +1767,11 @@
       <c r="C42" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="D42" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>61</v>
       </c>
@@ -2230,8 +1781,11 @@
       <c r="C43" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="D43" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>62</v>
       </c>
@@ -2241,8 +1795,11 @@
       <c r="C44" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="D44" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>64</v>
       </c>
@@ -2252,8 +1809,11 @@
       <c r="C45" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="D45" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>65</v>
       </c>
@@ -2263,8 +1823,11 @@
       <c r="C46" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="D46" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>68</v>
       </c>
@@ -2274,8 +1837,11 @@
       <c r="C47" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="D47" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>69</v>
       </c>
@@ -2285,8 +1851,11 @@
       <c r="C48" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="D48" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>70</v>
       </c>
@@ -2296,8 +1865,11 @@
       <c r="C49" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="D49" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>71</v>
       </c>
@@ -2307,8 +1879,11 @@
       <c r="C50" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="D50" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>72</v>
       </c>
@@ -2318,8 +1893,11 @@
       <c r="C51" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="D51" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>74</v>
       </c>
@@ -2329,8 +1907,11 @@
       <c r="C52" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="D52" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>75</v>
       </c>
@@ -2340,8 +1921,11 @@
       <c r="C53" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="D53" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>78</v>
       </c>
@@ -2351,8 +1935,11 @@
       <c r="C54" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="D54" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>79</v>
       </c>
@@ -2362,8 +1949,11 @@
       <c r="C55" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="D55" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>80</v>
       </c>
@@ -2373,8 +1963,11 @@
       <c r="C56" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="D56" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>81</v>
       </c>
@@ -2384,8 +1977,11 @@
       <c r="C57" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="D57" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>82</v>
       </c>
@@ -2395,8 +1991,11 @@
       <c r="C58" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="D58" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>84</v>
       </c>
@@ -2406,8 +2005,11 @@
       <c r="C59" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="D59" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>85</v>
       </c>
@@ -2417,8 +2019,11 @@
       <c r="C60" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="D60" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>88</v>
       </c>
@@ -2428,8 +2033,11 @@
       <c r="C61" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="D61" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>89</v>
       </c>
@@ -2439,8 +2047,11 @@
       <c r="C62" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="D62" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>90</v>
       </c>
@@ -2450,8 +2061,11 @@
       <c r="C63" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="D63" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>91</v>
       </c>
@@ -2461,8 +2075,11 @@
       <c r="C64" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="D64" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>92</v>
       </c>
@@ -2472,8 +2089,11 @@
       <c r="C65" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="D65" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>94</v>
       </c>
@@ -2483,8 +2103,11 @@
       <c r="C66" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="D66" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>95</v>
       </c>
@@ -2494,8 +2117,11 @@
       <c r="C67" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="D67" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>96</v>
       </c>
@@ -2505,8 +2131,11 @@
       <c r="C68" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="D68" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>99</v>
       </c>
@@ -2516,8 +2145,11 @@
       <c r="C69" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="D69" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>100</v>
       </c>
@@ -2527,8 +2159,11 @@
       <c r="C70" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="D70" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>101</v>
       </c>
@@ -2538,8 +2173,11 @@
       <c r="C71" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="D71" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>100</v>
       </c>
@@ -2549,8 +2187,11 @@
       <c r="C72" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="D72" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>103</v>
       </c>
@@ -2560,8 +2201,11 @@
       <c r="C73" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="74" spans="1:3">
+      <c r="D73" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>104</v>
       </c>
@@ -2571,8 +2215,11 @@
       <c r="C74" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="D74" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>107</v>
       </c>
@@ -2582,8 +2229,11 @@
       <c r="C75" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="D75" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>108</v>
       </c>
@@ -2593,8 +2243,11 @@
       <c r="C76" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="D76" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>109</v>
       </c>
@@ -2604,8 +2257,11 @@
       <c r="C77" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="78" spans="1:3">
+      <c r="D77" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>110</v>
       </c>
@@ -2615,8 +2271,11 @@
       <c r="C78" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="79" spans="1:3">
+      <c r="D78" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>112</v>
       </c>
@@ -2626,8 +2285,11 @@
       <c r="C79" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="D79" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>113</v>
       </c>
@@ -2637,8 +2299,11 @@
       <c r="C80" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="D80" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>116</v>
       </c>
@@ -2648,8 +2313,11 @@
       <c r="C81" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="D81" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>117</v>
       </c>
@@ -2659,8 +2327,11 @@
       <c r="C82" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="D82" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>118</v>
       </c>
@@ -2670,8 +2341,11 @@
       <c r="C83" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="D83" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>119</v>
       </c>
@@ -2681,8 +2355,11 @@
       <c r="C84" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="D84" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>113</v>
       </c>
@@ -2692,8 +2369,11 @@
       <c r="C85" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="D85" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>121</v>
       </c>
@@ -2703,8 +2383,11 @@
       <c r="C86" s="1" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="D86" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>122</v>
       </c>
@@ -2714,8 +2397,11 @@
       <c r="C87" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="D87" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>125</v>
       </c>
@@ -2725,8 +2411,11 @@
       <c r="C88" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="D88" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>126</v>
       </c>
@@ -2736,8 +2425,11 @@
       <c r="C89" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="D89" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>127</v>
       </c>
@@ -2747,8 +2439,11 @@
       <c r="C90" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="D90" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>128</v>
       </c>
@@ -2758,8 +2453,11 @@
       <c r="C91" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="D91" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>130</v>
       </c>
@@ -2769,8 +2467,11 @@
       <c r="C92" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="D92" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>133</v>
       </c>
@@ -2780,8 +2481,11 @@
       <c r="C93" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="D93" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>134</v>
       </c>
@@ -2791,8 +2495,11 @@
       <c r="C94" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="D94" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>135</v>
       </c>
@@ -2802,8 +2509,11 @@
       <c r="C95" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
+      <c r="D95" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>136</v>
       </c>
@@ -2813,8 +2523,11 @@
       <c r="C96" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="97" spans="1:3">
+      <c r="D96" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>138</v>
       </c>
@@ -2824,8 +2537,11 @@
       <c r="C97" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
+      <c r="D97" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>141</v>
       </c>
@@ -2835,8 +2551,11 @@
       <c r="C98" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="99" spans="1:3">
+      <c r="D98" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>142</v>
       </c>
@@ -2846,8 +2565,11 @@
       <c r="C99" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="100" spans="1:3">
+      <c r="D99" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>143</v>
       </c>
@@ -2857,8 +2579,11 @@
       <c r="C100" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="101" spans="1:3">
+      <c r="D100" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>144</v>
       </c>
@@ -2868,8 +2593,11 @@
       <c r="C101" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="102" spans="1:3">
+      <c r="D101" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>145</v>
       </c>
@@ -2879,8 +2607,11 @@
       <c r="C102" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="103" spans="1:3">
+      <c r="D102" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>147</v>
       </c>
@@ -2890,8 +2621,11 @@
       <c r="C103" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="104" spans="1:3">
+      <c r="D103" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>150</v>
       </c>
@@ -2901,8 +2635,11 @@
       <c r="C104" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="105" spans="1:3">
+      <c r="D104" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>151</v>
       </c>
@@ -2912,8 +2649,11 @@
       <c r="C105" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="106" spans="1:3">
+      <c r="D105" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>152</v>
       </c>
@@ -2923,8 +2663,11 @@
       <c r="C106" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="107" spans="1:3">
+      <c r="D106" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>153</v>
       </c>
@@ -2934,8 +2677,11 @@
       <c r="C107" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="108" spans="1:3">
+      <c r="D107" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>154</v>
       </c>
@@ -2945,8 +2691,11 @@
       <c r="C108" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="109" spans="1:3">
+      <c r="D108" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>156</v>
       </c>
@@ -2956,8 +2705,11 @@
       <c r="C109" s="1" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="110" spans="1:3">
+      <c r="D109" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>157</v>
       </c>
@@ -2967,8 +2719,11 @@
       <c r="C110" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="111" spans="1:3">
+      <c r="D110" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>160</v>
       </c>
@@ -2978,8 +2733,11 @@
       <c r="C111" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="112" spans="1:3">
+      <c r="D111" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>161</v>
       </c>
@@ -2989,8 +2747,11 @@
       <c r="C112" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="113" spans="1:3">
+      <c r="D112" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>162</v>
       </c>
@@ -3000,8 +2761,11 @@
       <c r="C113" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="114" spans="1:3">
+      <c r="D113" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>163</v>
       </c>
@@ -3011,8 +2775,11 @@
       <c r="C114" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="115" spans="1:3">
+      <c r="D114" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>164</v>
       </c>
@@ -3022,8 +2789,11 @@
       <c r="C115" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="116" spans="1:3">
+      <c r="D115" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>154</v>
       </c>
@@ -3033,8 +2803,11 @@
       <c r="C116" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="117" spans="1:3">
+      <c r="D116" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>156</v>
       </c>
@@ -3044,8 +2817,11 @@
       <c r="C117" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="118" spans="1:3">
+      <c r="D117" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>166</v>
       </c>
@@ -3055,8 +2831,11 @@
       <c r="C118" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="119" spans="1:3">
+      <c r="D118" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>169</v>
       </c>
@@ -3066,8 +2845,11 @@
       <c r="C119" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="120" spans="1:3">
+      <c r="D119" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>170</v>
       </c>
@@ -3077,8 +2859,11 @@
       <c r="C120" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="121" spans="1:3">
+      <c r="D120" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>171</v>
       </c>
@@ -3088,8 +2873,11 @@
       <c r="C121" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="122" spans="1:3">
+      <c r="D121" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>172</v>
       </c>
@@ -3099,8 +2887,11 @@
       <c r="C122" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="123" spans="1:3">
+      <c r="D122" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>173</v>
       </c>
@@ -3110,8 +2901,11 @@
       <c r="C123" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="124" spans="1:3">
+      <c r="D123" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>175</v>
       </c>
@@ -3121,8 +2915,11 @@
       <c r="C124" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="125" spans="1:3">
+      <c r="D124" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>178</v>
       </c>
@@ -3132,8 +2929,11 @@
       <c r="C125" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="126" spans="1:3">
+      <c r="D125" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>179</v>
       </c>
@@ -3143,8 +2943,11 @@
       <c r="C126" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="127" spans="1:3">
+      <c r="D126" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>180</v>
       </c>
@@ -3154,8 +2957,11 @@
       <c r="C127" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="128" spans="1:3">
+      <c r="D127" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>181</v>
       </c>
@@ -3165,8 +2971,11 @@
       <c r="C128" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="129" spans="1:3">
+      <c r="D128" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>182</v>
       </c>
@@ -3176,8 +2985,11 @@
       <c r="C129" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="130" spans="1:3">
+      <c r="D129" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>184</v>
       </c>
@@ -3187,8 +2999,11 @@
       <c r="C130" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="131" spans="1:3">
+      <c r="D130" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>185</v>
       </c>
@@ -3198,8 +3013,11 @@
       <c r="C131" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="132" spans="1:3">
+      <c r="D131" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>188</v>
       </c>
@@ -3209,8 +3027,11 @@
       <c r="C132" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="133" spans="1:3">
+      <c r="D132" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>189</v>
       </c>
@@ -3220,8 +3041,11 @@
       <c r="C133" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="134" spans="1:3">
+      <c r="D133" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>190</v>
       </c>
@@ -3231,8 +3055,11 @@
       <c r="C134" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="135" spans="1:3">
+      <c r="D134" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>191</v>
       </c>
@@ -3242,8 +3069,11 @@
       <c r="C135" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="136" spans="1:3">
+      <c r="D135" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>192</v>
       </c>
@@ -3253,8 +3083,11 @@
       <c r="C136" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="137" spans="1:3">
+      <c r="D136" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>194</v>
       </c>
@@ -3264,8 +3097,11 @@
       <c r="C137" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="138" spans="1:3">
+      <c r="D137" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>195</v>
       </c>
@@ -3275,8 +3111,11 @@
       <c r="C138" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="139" spans="1:3">
+      <c r="D138" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>198</v>
       </c>
@@ -3286,8 +3125,11 @@
       <c r="C139" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="140" spans="1:3">
+      <c r="D139" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>199</v>
       </c>
@@ -3297,8 +3139,11 @@
       <c r="C140" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="141" spans="1:3">
+      <c r="D140" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>200</v>
       </c>
@@ -3308,8 +3153,11 @@
       <c r="C141" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="142" spans="1:3">
+      <c r="D141" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>201</v>
       </c>
@@ -3319,8 +3167,11 @@
       <c r="C142" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="143" spans="1:3">
+      <c r="D142" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>203</v>
       </c>
@@ -3330,8 +3181,11 @@
       <c r="C143" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="144" spans="1:3">
+      <c r="D143" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>204</v>
       </c>
@@ -3341,8 +3195,11 @@
       <c r="C144" s="1" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="145" spans="1:3">
+      <c r="D144" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>207</v>
       </c>
@@ -3352,8 +3209,11 @@
       <c r="C145" s="1" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="146" spans="1:3">
+      <c r="D145" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>208</v>
       </c>
@@ -3363,8 +3223,11 @@
       <c r="C146" s="1" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="147" spans="1:3">
+      <c r="D146" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>209</v>
       </c>
@@ -3374,8 +3237,11 @@
       <c r="C147" s="1" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="148" spans="1:3">
+      <c r="D147" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>210</v>
       </c>
@@ -3385,8 +3251,11 @@
       <c r="C148" s="1" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="149" spans="1:3">
+      <c r="D148" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>211</v>
       </c>
@@ -3396,8 +3265,11 @@
       <c r="C149" s="1" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="150" spans="1:3">
+      <c r="D149" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>213</v>
       </c>
@@ -3407,8 +3279,11 @@
       <c r="C150" s="1" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="151" spans="1:3">
+      <c r="D150" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>214</v>
       </c>
@@ -3418,8 +3293,11 @@
       <c r="C151" s="1" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="152" spans="1:3">
+      <c r="D151" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>217</v>
       </c>
@@ -3429,8 +3307,11 @@
       <c r="C152" s="1" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="153" spans="1:3">
+      <c r="D152" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>218</v>
       </c>
@@ -3440,8 +3321,11 @@
       <c r="C153" s="1" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="154" spans="1:3">
+      <c r="D153" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>219</v>
       </c>
@@ -3451,8 +3335,11 @@
       <c r="C154" s="1" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="155" spans="1:3">
+      <c r="D154" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>220</v>
       </c>
@@ -3462,8 +3349,11 @@
       <c r="C155" s="1" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="156" spans="1:3">
+      <c r="D155" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>221</v>
       </c>
@@ -3473,8 +3363,11 @@
       <c r="C156" s="1" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="157" spans="1:3">
+      <c r="D156" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>223</v>
       </c>
@@ -3484,8 +3377,11 @@
       <c r="C157" s="1" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="158" spans="1:3">
+      <c r="D157" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>224</v>
       </c>
@@ -3495,8 +3391,11 @@
       <c r="C158" s="1" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="159" spans="1:3">
+      <c r="D158" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>227</v>
       </c>
@@ -3506,8 +3405,11 @@
       <c r="C159" s="1" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="160" spans="1:3">
+      <c r="D159" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>228</v>
       </c>
@@ -3517,8 +3419,11 @@
       <c r="C160" s="1" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="161" spans="1:3">
+      <c r="D160" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>229</v>
       </c>
@@ -3528,8 +3433,11 @@
       <c r="C161" s="1" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="162" spans="1:3">
+      <c r="D161" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>230</v>
       </c>
@@ -3539,32 +3447,41 @@
       <c r="C162" s="1" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="163" spans="1:3">
+      <c r="D162" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A164" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3">
-      <c r="A164" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3">
-      <c r="A165" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>232</v>
@@ -3572,10 +3489,13 @@
       <c r="C165" s="1" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="166" spans="1:3">
+      <c r="D165" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>232</v>
@@ -3583,10 +3503,13 @@
       <c r="C166" s="1" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="167" spans="1:3">
+      <c r="D166" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>232</v>
@@ -3594,86 +3517,194 @@
       <c r="C167" s="1" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="168" spans="1:3">
+      <c r="D167" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A169" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A171" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A172" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3">
-      <c r="A169" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3">
-      <c r="A170" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3">
-      <c r="A171" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
-      <c r="A172" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C172" s="3" t="s">
+      <c r="C172" s="1" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="173" spans="1:3">
+      <c r="D172" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C173" s="3" t="s">
+      <c r="C173" s="1" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="174" spans="1:3">
+      <c r="D173" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C174" s="3" t="s">
+      <c r="C174" s="1" t="s">
         <v>240</v>
       </c>
+      <c r="D174" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A175" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A176" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A177" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A178" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A179" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A180" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>252</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>